--- a/questions.template.xlsx
+++ b/questions.template.xlsx
@@ -362,7 +362,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Which format the row is. Pick one from the list. Leave it blank for multiple choice, or for the shorthand: a row with no options becomes a typed answer, or true/false when the answer is True or False. Spellings like True/False, TF or Select all that apply work too, but a word the game does not know makes the row multiple choice.</t>
+        <t>Which format the row is. Pick one from the list. Leave it blank for multiple choice, or for the shorthand: a row with no options becomes a typed answer, or true/false when the answer is True or False. Spellings like True/False, TF, Select all that apply or Puzzle · order work too, but a word the game does not know leaves the row out as an unknown format.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Select all that apply, Multiple select, Checkbox</t>
+          <t>Select all that apply, Multiple select, Checkboxes</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Type, Short answer, Free text</t>
+          <t>Typed answer, Short answer, Fill in the blank, Free text</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Closest, Estimate, Guess</t>
+          <t>Closest, Closest guess, Estimate, Guess</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Order, Sequence, Rank, Timeline</t>
+          <t>Puzzle · order, Order, Sequence, Rank, Timeline</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Matching, Pairs, Connect</t>
+          <t>Puzzle · match, Matching, Pairs, Connect</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Sort, Group, Buckets, Classify</t>
+          <t>Puzzle · sort, Sort, Group, Buckets, Classify</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Unscramble, Anagram, Jumble</t>
+          <t>Puzzle · unscramble, Unscramble, Anagram, Jumble</t>
         </is>
       </c>
     </row>

--- a/questions.template.xlsx
+++ b/questions.template.xlsx
@@ -427,7 +427,7 @@
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>SLIDER, RANGE and NUMBER only: what the number counts, shown after it (km, m, years, °F).</t>
+        <t>SLIDER, RANGE and NUMBER only: what the number counts, shown after it (km, m, °F, or years for a span of years). Leave it blank for a calendar year, or 1969 shows as 1,969 years.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1960</v>
+        <v>1940</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1980</v>
@@ -1744,13 +1744,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the twelve names" error="Other spellings like TF or Select all that apply still import. Check the Question types tab." promptTitle="Format" prompt="Pick a format, or leave blank for multiple choice." type="list" errorStyle="warning">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the twelve names" error="Other spellings like TF or Select all that apply still import. Check the Question types tab." promptTitle="Format" prompt="Pick a format, or leave blank for multiple choice." type="list" errorStyle="warning">
       <formula1>"MULTIPLE_CHOICE,MULTI_SELECT,TRUE_FALSE,TYPE_ANSWER,SLIDER,RANGE,NUMBER,PIN,PUZZLE,MATCH,CATEGORIZE,SCRAMBLE"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="margin is none, low, medium, high or maximum." promptTitle="Margin" prompt="SLIDER, NUMBER and PIN: how much a near miss scores." type="list" errorStyle="warning">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="margin is none, low, medium, high or maximum." promptTitle="Margin" prompt="SLIDER, NUMBER and PIN: how much a near miss scores." type="list" errorStyle="warning">
       <formula1>"none,low,medium,high,maximum"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="The clock runs from 5 to 120 seconds." promptTitle="Seconds" prompt="Blank uses the format's own clock." type="whole" errorStyle="warning" operator="between">
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="The clock runs from 5 to 120 seconds." promptTitle="Seconds" prompt="Blank uses the format's own clock." type="whole" errorStyle="warning" operator="between">
       <formula1>5</formula1>
       <formula2>120</formula2>
     </dataValidation>
@@ -1835,7 +1835,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>In Google Sheets: File → Save as Google Sheets, or File → Import into a sheet of your own, then share and paste the link the same way. To use a different tab, open it and copy the URL from the address bar.</t>
+          <t>In Google Sheets: File → Save as Google Sheets, then share and paste the link the same way. If you import it into a spreadsheet you already have (File → Import → Insert new sheet(s)), open the Questions tab and paste the URL from the address bar (it ends in gid=…): a plain share link reads that spreadsheet's original tab.</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• A row that cannot be played is left out, and the import screen says which and why. Check the review screen shows the number of questions you expect.</t>
+          <t>• A row that cannot be played is left out. The review screen says how many and why (the first few row numbers are in the browser's console), so check it shows the number of questions you expect.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ignored once the options are filled in; with none, the answer and each part of a comma list are accepted</t>
+          <t>Required, but not graded once the options are filled in: repeat option1. With none, the answer and each part of a comma list are accepted</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>All or nothing; case and extra spaces ignored, spelling and accents not</t>
+          <t>All or nothing. One accepted spelling, or several in any order (a, b and c) when every one is accepted; case, curly quotes and extra spaces ignored, spelling and accents not</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>The answer the reveal shows. With only three options: the answer, or a band like 1968-1970</t>
+          <t>Required, but not graded or shown when option4 and option5 are filled in: the reveal shows that band. With only three options: the answer, or a band like 1968-1970 with nothing after it (a unit goes in the unit column)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>The exact answer (or a band like 8800-8900)</t>
+          <t>The exact answer, or a band like 8800-8900 with nothing after it (a unit goes in the unit column)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ignored when the options are filled in. With none: the order, joined with |</t>
+          <t>Required, but not graded when the options are filled in: write the order again. With none: the order, joined with | (the type column must say PUZZLE)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">

--- a/questions.template.xlsx
+++ b/questions.template.xlsx
@@ -432,7 +432,7 @@
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Optional: seconds on the clock for this question, 5 to 120. Blank uses the format's own clock.</t>
+        <t>Optional: seconds on the clock for this question, 5 to 120. Blank uses the format's own clock, plus reading time for a long question.</t>
       </text>
     </comment>
   </commentList>
@@ -1602,7 +1602,7 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>20s</t>
+          <t>25s</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>20s</t>
+          <t>25s</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>20s</t>
+          <t>25s</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>20s</t>
+          <t>25s</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>20s</t>
+          <t>25s</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>25s</t>
+          <t>35s</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>45s</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>45s</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>45s</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>25s</t>
+          <t>35s</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>12s / 20s</t>
+          <t>12s / 25s</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
